--- a/output/pdf_financials_xlsx/LCR.xlsx
+++ b/output/pdf_financials_xlsx/LCR.xlsx
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>-0.13703</v>
+        <v>-0.24613</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>-0.174405</v>
@@ -4930,7 +4930,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E73" s="5" t="n">
         <v>-0.1091</v>
       </c>

--- a/output/pdf_financials_xlsx/LCR.xlsx
+++ b/output/pdf_financials_xlsx/LCR.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.24173</v>
+        <v>0.923986</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.750729</v>
+        <v>1.901428</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.449703</v>
+        <v>1.064084</v>
       </c>
     </row>
     <row r="11">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">

--- a/output/pdf_financials_xlsx/LCR.xlsx
+++ b/output/pdf_financials_xlsx/LCR.xlsx
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-3.102687</v>
+        <v>-3.102187</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-3.608456</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-3.102687</v>
+        <v>-3.102187</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-3.608456</v>
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.065953</v>
       </c>
     </row>
     <row r="116">
@@ -4343,7 +4343,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -4690,7 +4694,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>-3.102187</v>
       </c>
@@ -6980,7 +6988,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E139" s="5" t="n">
         <v>-3.102187</v>
       </c>
@@ -7009,7 +7021,11 @@
           <t>Net loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E140" s="5" t="n">
         <v>-0.0005</v>
       </c>
